--- a/artfynd/A 24423-2026 artfynd.xlsx
+++ b/artfynd/A 24423-2026 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133828201</v>
+        <v>133828208</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519061</v>
+        <v>519108</v>
       </c>
       <c r="R4" t="n">
-        <v>6906118</v>
+        <v>6906047</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,32 +1009,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133828208</v>
+        <v>133828213</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>83327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519108</v>
+        <v>519134</v>
       </c>
       <c r="R5" t="n">
-        <v>6906047</v>
+        <v>6906052</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,32 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133828213</v>
+        <v>133828224</v>
       </c>
       <c r="B6" t="n">
-        <v>83327</v>
+        <v>83344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519134</v>
+        <v>519158</v>
       </c>
       <c r="R6" t="n">
-        <v>6906052</v>
+        <v>6906007</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133828206</v>
+        <v>133828238</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,13 +1258,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519089</v>
+        <v>519321</v>
       </c>
       <c r="R7" t="n">
-        <v>6906079</v>
+        <v>6905895</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,12 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>35 ex</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,32 +1330,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133828224</v>
+        <v>133828206</v>
       </c>
       <c r="B8" t="n">
-        <v>83344</v>
+        <v>99181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519158</v>
+        <v>519089</v>
       </c>
       <c r="R8" t="n">
-        <v>6906007</v>
+        <v>6906079</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1410,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133828238</v>
+        <v>133828190</v>
       </c>
       <c r="B9" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,34 +1453,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519321</v>
+        <v>519017</v>
       </c>
       <c r="R9" t="n">
-        <v>6905895</v>
+        <v>6906239</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1525,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1530,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133828190</v>
+        <v>133828201</v>
       </c>
       <c r="B10" t="n">
         <v>57975</v>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519017</v>
+        <v>519061</v>
       </c>
       <c r="R10" t="n">
-        <v>6906239</v>
+        <v>6906118</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1682,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133828230</v>
+        <v>133828240</v>
       </c>
       <c r="B11" t="n">
         <v>99181</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519227</v>
+        <v>519318</v>
       </c>
       <c r="R11" t="n">
-        <v>6905953</v>
+        <v>6905855</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133828240</v>
+        <v>133828230</v>
       </c>
       <c r="B12" t="n">
         <v>99181</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519318</v>
+        <v>519227</v>
       </c>
       <c r="R12" t="n">
-        <v>6905855</v>
+        <v>6905953</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2130,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828196</v>
+        <v>133828214</v>
       </c>
       <c r="B15" t="n">
-        <v>83344</v>
+        <v>80485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519042</v>
+        <v>519137</v>
       </c>
       <c r="R15" t="n">
-        <v>6906192</v>
+        <v>6906050</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,32 +2237,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828214</v>
+        <v>133828199</v>
       </c>
       <c r="B16" t="n">
-        <v>80485</v>
+        <v>89340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519137</v>
+        <v>519034</v>
       </c>
       <c r="R16" t="n">
-        <v>6906050</v>
+        <v>6906130</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828199</v>
+        <v>133828196</v>
       </c>
       <c r="B17" t="n">
-        <v>89340</v>
+        <v>83344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519034</v>
+        <v>519042</v>
       </c>
       <c r="R17" t="n">
-        <v>6906130</v>
+        <v>6906192</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133828236</v>
+        <v>133828194</v>
       </c>
       <c r="B19" t="n">
-        <v>98046</v>
+        <v>99181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519308</v>
+        <v>519039</v>
       </c>
       <c r="R19" t="n">
-        <v>6905887</v>
+        <v>6906208</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>12 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,32 +2777,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133828194</v>
+        <v>133828236</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>98046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2807,13 +2812,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519039</v>
+        <v>519308</v>
       </c>
       <c r="R21" t="n">
-        <v>6906208</v>
+        <v>6905887</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2842,7 +2847,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2852,12 +2857,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>12 ex</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828356</v>
+        <v>133828242</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,42 +3007,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518990</v>
+        <v>519341</v>
       </c>
       <c r="R23" t="n">
-        <v>6906191</v>
+        <v>6905850</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3074,7 +3066,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3084,12 +3076,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828242</v>
+        <v>133828192</v>
       </c>
       <c r="B24" t="n">
-        <v>83344</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3127,21 +3114,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3151,10 +3138,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519341</v>
+        <v>519016</v>
       </c>
       <c r="R24" t="n">
-        <v>6905850</v>
+        <v>6906224</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3186,7 +3173,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,7 +3183,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,10 +3317,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828192</v>
+        <v>133828356</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,34 +3328,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519016</v>
+        <v>518990</v>
       </c>
       <c r="R26" t="n">
-        <v>6906224</v>
+        <v>6906191</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3395,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3405,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828193</v>
+        <v>133828198</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,45 +3555,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519027</v>
+        <v>519034</v>
       </c>
       <c r="R28" t="n">
-        <v>6906216</v>
+        <v>6906126</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3622,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3632,12 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,48 +3758,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828184</v>
+        <v>133828193</v>
       </c>
       <c r="B30" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518977</v>
+        <v>519027</v>
       </c>
       <c r="R30" t="n">
-        <v>6906242</v>
+        <v>6906216</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3841,7 +3836,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3851,7 +3846,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,32 +3990,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828198</v>
+        <v>133828184</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>91923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519034</v>
+        <v>518977</v>
       </c>
       <c r="R32" t="n">
-        <v>6906126</v>
+        <v>6906242</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,32 +4204,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828233</v>
+        <v>133828218</v>
       </c>
       <c r="B34" t="n">
-        <v>83344</v>
+        <v>80479</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519272</v>
+        <v>519135</v>
       </c>
       <c r="R34" t="n">
-        <v>6905906</v>
+        <v>6906035</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4311,32 +4311,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828197</v>
+        <v>133828207</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>80479</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519032</v>
+        <v>519112</v>
       </c>
       <c r="R35" t="n">
-        <v>6906144</v>
+        <v>6906067</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4418,32 +4418,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828218</v>
+        <v>133828233</v>
       </c>
       <c r="B36" t="n">
-        <v>80479</v>
+        <v>83344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519135</v>
+        <v>519272</v>
       </c>
       <c r="R36" t="n">
-        <v>6906035</v>
+        <v>6905906</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,45 +4525,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828207</v>
+        <v>133828231</v>
       </c>
       <c r="B37" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519112</v>
+        <v>519254</v>
       </c>
       <c r="R37" t="n">
-        <v>6906067</v>
+        <v>6905931</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4595,7 +4603,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4605,7 +4613,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,10 +4645,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828231</v>
+        <v>133828197</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4643,42 +4656,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519254</v>
+        <v>519032</v>
       </c>
       <c r="R38" t="n">
-        <v>6905931</v>
+        <v>6906144</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4710,7 +4715,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4720,12 +4725,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4864,7 +4864,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828226</v>
+        <v>133828191</v>
       </c>
       <c r="B40" t="n">
         <v>99181</v>
@@ -4899,13 +4899,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519204</v>
+        <v>519018</v>
       </c>
       <c r="R40" t="n">
-        <v>6905970</v>
+        <v>6906233</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4976,32 +4976,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828222</v>
+        <v>133828226</v>
       </c>
       <c r="B41" t="n">
-        <v>79117</v>
+        <v>99181</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519147</v>
+        <v>519204</v>
       </c>
       <c r="R41" t="n">
-        <v>6906035</v>
+        <v>6905970</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5056,7 +5056,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5083,32 +5088,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828191</v>
+        <v>133828222</v>
       </c>
       <c r="B42" t="n">
-        <v>99181</v>
+        <v>79117</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5118,13 +5123,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519018</v>
+        <v>519147</v>
       </c>
       <c r="R42" t="n">
-        <v>6906233</v>
+        <v>6906035</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,7 +5158,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5163,12 +5168,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,32 +5195,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828232</v>
+        <v>133828239</v>
       </c>
       <c r="B43" t="n">
-        <v>80424</v>
+        <v>79359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519261</v>
+        <v>519321</v>
       </c>
       <c r="R43" t="n">
-        <v>6905908</v>
+        <v>6905865</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5302,32 +5302,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828239</v>
+        <v>133828232</v>
       </c>
       <c r="B44" t="n">
-        <v>79359</v>
+        <v>80424</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519321</v>
+        <v>519261</v>
       </c>
       <c r="R44" t="n">
-        <v>6905865</v>
+        <v>6905908</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5409,56 +5409,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828205</v>
+        <v>133828186</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519093</v>
+        <v>518978</v>
       </c>
       <c r="R45" t="n">
-        <v>6906086</v>
+        <v>6906247</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5487,7 +5479,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5497,12 +5489,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5529,48 +5521,56 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828186</v>
+        <v>133828205</v>
       </c>
       <c r="B46" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518978</v>
+        <v>519093</v>
       </c>
       <c r="R46" t="n">
-        <v>6906247</v>
+        <v>6906086</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828183</v>
+        <v>133828211</v>
       </c>
       <c r="B49" t="n">
-        <v>91960</v>
+        <v>83344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518971</v>
+        <v>519116</v>
       </c>
       <c r="R49" t="n">
-        <v>6906249</v>
+        <v>6906040</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5975,10 +5975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828211</v>
+        <v>133828183</v>
       </c>
       <c r="B50" t="n">
-        <v>83344</v>
+        <v>91960</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519116</v>
+        <v>518971</v>
       </c>
       <c r="R50" t="n">
-        <v>6906040</v>
+        <v>6906249</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6082,10 +6082,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828223</v>
+        <v>133828355</v>
       </c>
       <c r="B51" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6093,34 +6093,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519161</v>
+        <v>518990</v>
       </c>
       <c r="R51" t="n">
-        <v>6906027</v>
+        <v>6906188</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6152,7 +6160,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6162,7 +6170,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6309,10 +6322,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828355</v>
+        <v>133828223</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,42 +6333,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518990</v>
+        <v>519161</v>
       </c>
       <c r="R53" t="n">
-        <v>6906188</v>
+        <v>6906027</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6387,7 +6392,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6397,12 +6402,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6536,32 +6536,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828204</v>
+        <v>133828202</v>
       </c>
       <c r="B55" t="n">
-        <v>80479</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519091</v>
+        <v>519066</v>
       </c>
       <c r="R55" t="n">
-        <v>6906091</v>
+        <v>6906112</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6643,32 +6643,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828237</v>
+        <v>133828181</v>
       </c>
       <c r="B56" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519323</v>
+        <v>518950</v>
       </c>
       <c r="R56" t="n">
-        <v>6905894</v>
+        <v>6906228</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6723,7 +6723,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6750,32 +6755,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828181</v>
+        <v>133828237</v>
       </c>
       <c r="B57" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6785,13 +6790,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518950</v>
+        <v>519323</v>
       </c>
       <c r="R57" t="n">
-        <v>6906228</v>
+        <v>6905894</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6820,7 +6825,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6830,12 +6835,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6862,32 +6862,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828202</v>
+        <v>133828204</v>
       </c>
       <c r="B58" t="n">
-        <v>79359</v>
+        <v>80479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519066</v>
+        <v>519091</v>
       </c>
       <c r="R58" t="n">
-        <v>6906112</v>
+        <v>6906091</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6969,32 +6969,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828200</v>
+        <v>133828221</v>
       </c>
       <c r="B59" t="n">
-        <v>99181</v>
+        <v>83344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7004,13 +7004,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519034</v>
+        <v>519140</v>
       </c>
       <c r="R59" t="n">
-        <v>6906128</v>
+        <v>6906024</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7049,12 +7049,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7081,32 +7076,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828221</v>
+        <v>133828200</v>
       </c>
       <c r="B60" t="n">
-        <v>83344</v>
+        <v>99181</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7116,13 +7111,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519140</v>
+        <v>519034</v>
       </c>
       <c r="R60" t="n">
-        <v>6906024</v>
+        <v>6906128</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7151,7 +7146,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7161,7 +7156,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 24423-2026 artfynd.xlsx
+++ b/artfynd/A 24423-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>133828243</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133828208</v>
+        <v>133828224</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>83351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519108</v>
+        <v>519158</v>
       </c>
       <c r="R4" t="n">
-        <v>6906047</v>
+        <v>6906007</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,32 +1009,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133828213</v>
+        <v>133828208</v>
       </c>
       <c r="B5" t="n">
-        <v>83327</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519134</v>
+        <v>519108</v>
       </c>
       <c r="R5" t="n">
-        <v>6906052</v>
+        <v>6906047</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133828224</v>
+        <v>133828201</v>
       </c>
       <c r="B6" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,34 +1127,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519158</v>
+        <v>519061</v>
       </c>
       <c r="R6" t="n">
-        <v>6906007</v>
+        <v>6906118</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133828238</v>
+        <v>133828190</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,34 +1247,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519321</v>
+        <v>519017</v>
       </c>
       <c r="R7" t="n">
-        <v>6905895</v>
+        <v>6906239</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -1293,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,32 +1356,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133828206</v>
+        <v>133828213</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>83334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519089</v>
+        <v>519134</v>
       </c>
       <c r="R8" t="n">
-        <v>6906079</v>
+        <v>6906052</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,12 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>35 ex</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,56 +1463,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133828190</v>
+        <v>133828206</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519017</v>
+        <v>519089</v>
       </c>
       <c r="R9" t="n">
-        <v>6906239</v>
+        <v>6906079</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133828201</v>
+        <v>133828238</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>80481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,45 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519061</v>
+        <v>519321</v>
       </c>
       <c r="R10" t="n">
-        <v>6906118</v>
+        <v>6905895</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,12 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,7 +1685,7 @@
         <v>133828240</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>133828230</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>133828203</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>133828209</v>
       </c>
       <c r="B14" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828214</v>
+        <v>133828196</v>
       </c>
       <c r="B15" t="n">
-        <v>80485</v>
+        <v>83351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519137</v>
+        <v>519042</v>
       </c>
       <c r="R15" t="n">
-        <v>6906050</v>
+        <v>6906192</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,32 +2237,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828199</v>
+        <v>133828214</v>
       </c>
       <c r="B16" t="n">
-        <v>89340</v>
+        <v>80492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519034</v>
+        <v>519137</v>
       </c>
       <c r="R16" t="n">
-        <v>6906130</v>
+        <v>6906050</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828196</v>
+        <v>133828199</v>
       </c>
       <c r="B17" t="n">
-        <v>83344</v>
+        <v>89347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519042</v>
+        <v>519034</v>
       </c>
       <c r="R17" t="n">
-        <v>6906192</v>
+        <v>6906130</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,7 +2454,7 @@
         <v>133828212</v>
       </c>
       <c r="B18" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133828194</v>
+        <v>133828236</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>98053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519039</v>
+        <v>519308</v>
       </c>
       <c r="R19" t="n">
-        <v>6906208</v>
+        <v>6905887</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,12 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>12 ex</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,7 +2668,7 @@
         <v>133828188</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,32 +2772,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133828236</v>
+        <v>133828194</v>
       </c>
       <c r="B21" t="n">
-        <v>98046</v>
+        <v>99188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2812,13 +2807,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519308</v>
+        <v>519039</v>
       </c>
       <c r="R21" t="n">
-        <v>6905887</v>
+        <v>6906208</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,7 +2842,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2857,7 +2852,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>12 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,7 +2887,7 @@
         <v>133828182</v>
       </c>
       <c r="B22" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828242</v>
+        <v>133828356</v>
       </c>
       <c r="B23" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,34 +3007,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519341</v>
+        <v>518990</v>
       </c>
       <c r="R23" t="n">
-        <v>6905850</v>
+        <v>6906191</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3066,7 +3074,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3076,7 +3084,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3103,10 +3116,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828192</v>
+        <v>133828242</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>83351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,21 +3127,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3138,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519016</v>
+        <v>519341</v>
       </c>
       <c r="R24" t="n">
-        <v>6906224</v>
+        <v>6905850</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3173,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3183,7 +3196,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,7 +3226,7 @@
         <v>133828216</v>
       </c>
       <c r="B25" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,10 +3330,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828356</v>
+        <v>133828192</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3328,42 +3341,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518990</v>
+        <v>519016</v>
       </c>
       <c r="R26" t="n">
-        <v>6906191</v>
+        <v>6906224</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3395,7 +3400,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3405,12 +3410,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,32 +3437,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828227</v>
+        <v>133828180</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>80486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519206</v>
+        <v>518951</v>
       </c>
       <c r="R27" t="n">
-        <v>6905965</v>
+        <v>6906219</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828198</v>
+        <v>133828227</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519034</v>
+        <v>519206</v>
       </c>
       <c r="R28" t="n">
-        <v>6906126</v>
+        <v>6905965</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,48 +3651,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828180</v>
+        <v>133828193</v>
       </c>
       <c r="B29" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518951</v>
+        <v>519027</v>
       </c>
       <c r="R29" t="n">
-        <v>6906219</v>
+        <v>6906216</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,7 +3729,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3731,7 +3739,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3758,56 +3771,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828193</v>
+        <v>133828184</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>91930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519027</v>
+        <v>518977</v>
       </c>
       <c r="R30" t="n">
-        <v>6906216</v>
+        <v>6906242</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3836,7 +3841,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3846,12 +3851,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,7 +3881,7 @@
         <v>133828217</v>
       </c>
       <c r="B31" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3990,32 +3990,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828184</v>
+        <v>133828198</v>
       </c>
       <c r="B32" t="n">
-        <v>91923</v>
+        <v>79123</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518977</v>
+        <v>519034</v>
       </c>
       <c r="R32" t="n">
-        <v>6906242</v>
+        <v>6906126</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4100,7 +4100,7 @@
         <v>133828235</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4204,45 +4204,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828218</v>
+        <v>133828231</v>
       </c>
       <c r="B34" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519135</v>
+        <v>519254</v>
       </c>
       <c r="R34" t="n">
-        <v>6906035</v>
+        <v>6905931</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4274,7 +4282,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4284,7 +4292,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4311,32 +4324,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828207</v>
+        <v>133828233</v>
       </c>
       <c r="B35" t="n">
-        <v>80479</v>
+        <v>83351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4346,10 +4359,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519112</v>
+        <v>519272</v>
       </c>
       <c r="R35" t="n">
-        <v>6906067</v>
+        <v>6905906</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4381,7 +4394,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4391,7 +4404,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4418,10 +4431,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828233</v>
+        <v>133828197</v>
       </c>
       <c r="B36" t="n">
-        <v>83344</v>
+        <v>79366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,21 +4442,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4453,10 +4466,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519272</v>
+        <v>519032</v>
       </c>
       <c r="R36" t="n">
-        <v>6905906</v>
+        <v>6906144</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4488,7 +4501,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4498,7 +4511,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,53 +4538,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828231</v>
+        <v>133828218</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>80486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519254</v>
+        <v>519135</v>
       </c>
       <c r="R37" t="n">
-        <v>6905931</v>
+        <v>6906035</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4603,7 +4608,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4613,12 +4618,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4645,32 +4645,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828197</v>
+        <v>133828207</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>80486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519032</v>
+        <v>519112</v>
       </c>
       <c r="R38" t="n">
-        <v>6906144</v>
+        <v>6906067</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4755,7 +4755,7 @@
         <v>133828241</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828191</v>
+        <v>133828226</v>
       </c>
       <c r="B40" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,13 +4899,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519018</v>
+        <v>519204</v>
       </c>
       <c r="R40" t="n">
-        <v>6906233</v>
+        <v>6905970</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4976,32 +4976,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828226</v>
+        <v>133828222</v>
       </c>
       <c r="B41" t="n">
-        <v>99181</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519204</v>
+        <v>519147</v>
       </c>
       <c r="R41" t="n">
-        <v>6905970</v>
+        <v>6906035</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5056,12 +5056,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5088,32 +5083,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828222</v>
+        <v>133828191</v>
       </c>
       <c r="B42" t="n">
-        <v>79117</v>
+        <v>99188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5123,13 +5118,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519147</v>
+        <v>519018</v>
       </c>
       <c r="R42" t="n">
-        <v>6906035</v>
+        <v>6906233</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5158,7 +5153,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5168,7 +5163,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,32 +5195,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828239</v>
+        <v>133828232</v>
       </c>
       <c r="B43" t="n">
-        <v>79359</v>
+        <v>80431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519321</v>
+        <v>519261</v>
       </c>
       <c r="R43" t="n">
-        <v>6905865</v>
+        <v>6905908</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5302,32 +5302,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828232</v>
+        <v>133828239</v>
       </c>
       <c r="B44" t="n">
-        <v>80424</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519261</v>
+        <v>519321</v>
       </c>
       <c r="R44" t="n">
-        <v>6905908</v>
+        <v>6905865</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,7 +5412,7 @@
         <v>133828186</v>
       </c>
       <c r="B45" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5641,48 +5641,56 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828234</v>
+        <v>133828187</v>
       </c>
       <c r="B47" t="n">
-        <v>80424</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519302</v>
+        <v>518978</v>
       </c>
       <c r="R47" t="n">
-        <v>6905898</v>
+        <v>6906255</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5711,7 +5719,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5721,7 +5729,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5748,56 +5761,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828187</v>
+        <v>133828234</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>80431</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518978</v>
+        <v>519302</v>
       </c>
       <c r="R48" t="n">
-        <v>6906255</v>
+        <v>6905898</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5826,7 +5831,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5836,12 +5841,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828211</v>
+        <v>133828183</v>
       </c>
       <c r="B49" t="n">
-        <v>83344</v>
+        <v>91967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519116</v>
+        <v>518971</v>
       </c>
       <c r="R49" t="n">
-        <v>6906040</v>
+        <v>6906249</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5975,10 +5975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828183</v>
+        <v>133828211</v>
       </c>
       <c r="B50" t="n">
-        <v>91960</v>
+        <v>83351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518971</v>
+        <v>519116</v>
       </c>
       <c r="R50" t="n">
-        <v>6906249</v>
+        <v>6906040</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6082,10 +6082,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828355</v>
+        <v>133828223</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>83351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6093,42 +6093,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518990</v>
+        <v>519161</v>
       </c>
       <c r="R51" t="n">
-        <v>6906188</v>
+        <v>6906027</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6160,7 +6152,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6170,12 +6162,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6322,10 +6309,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828223</v>
+        <v>133828355</v>
       </c>
       <c r="B53" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6333,34 +6320,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519161</v>
+        <v>518990</v>
       </c>
       <c r="R53" t="n">
-        <v>6906027</v>
+        <v>6906188</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6392,7 +6387,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6402,7 +6397,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6432,7 +6432,7 @@
         <v>133828189</v>
       </c>
       <c r="B54" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6536,32 +6536,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828202</v>
+        <v>133828204</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>80486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519066</v>
+        <v>519091</v>
       </c>
       <c r="R55" t="n">
-        <v>6906112</v>
+        <v>6906091</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6643,32 +6643,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828181</v>
+        <v>133828237</v>
       </c>
       <c r="B56" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518950</v>
+        <v>519323</v>
       </c>
       <c r="R56" t="n">
-        <v>6906228</v>
+        <v>6905894</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6723,12 +6723,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6755,32 +6750,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828237</v>
+        <v>133828181</v>
       </c>
       <c r="B57" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6790,13 +6785,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519323</v>
+        <v>518950</v>
       </c>
       <c r="R57" t="n">
-        <v>6905894</v>
+        <v>6906228</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6825,7 +6820,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6835,7 +6830,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6862,32 +6862,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828204</v>
+        <v>133828202</v>
       </c>
       <c r="B58" t="n">
-        <v>80479</v>
+        <v>79366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519091</v>
+        <v>519066</v>
       </c>
       <c r="R58" t="n">
-        <v>6906091</v>
+        <v>6906112</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,7 +6972,7 @@
         <v>133828221</v>
       </c>
       <c r="B59" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>133828200</v>
       </c>
       <c r="B60" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>133828220</v>
       </c>
       <c r="B61" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 24423-2026 artfynd.xlsx
+++ b/artfynd/A 24423-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133828244</v>
+        <v>133828243</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519361</v>
+        <v>519347</v>
       </c>
       <c r="R2" t="n">
         <v>6905851</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133828243</v>
+        <v>133828244</v>
       </c>
       <c r="B3" t="n">
-        <v>79123</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,31 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519347</v>
+        <v>519361</v>
       </c>
       <c r="R3" t="n">
         <v>6905851</v>
@@ -865,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133828224</v>
+        <v>133828199</v>
       </c>
       <c r="B4" t="n">
-        <v>83351</v>
+        <v>89354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519158</v>
+        <v>519034</v>
       </c>
       <c r="R4" t="n">
-        <v>6906007</v>
+        <v>6906130</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133828208</v>
+        <v>133828183</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519108</v>
+        <v>518971</v>
       </c>
       <c r="R5" t="n">
-        <v>6906047</v>
+        <v>6906249</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133828201</v>
+        <v>133828212</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1127,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519061</v>
+        <v>519127</v>
       </c>
       <c r="R6" t="n">
-        <v>6906118</v>
+        <v>6906051</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,53 +1223,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133828190</v>
+        <v>133828184</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519017</v>
+        <v>518977</v>
       </c>
       <c r="R7" t="n">
-        <v>6906239</v>
+        <v>6906242</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
@@ -1314,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,32 +1330,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133828213</v>
+        <v>133828188</v>
       </c>
       <c r="B8" t="n">
-        <v>83334</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,13 +1365,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519134</v>
+        <v>518978</v>
       </c>
       <c r="R8" t="n">
-        <v>6906052</v>
+        <v>6906255</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133828206</v>
+        <v>133828192</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519089</v>
+        <v>519016</v>
       </c>
       <c r="R9" t="n">
-        <v>6906079</v>
+        <v>6906224</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>35 ex</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,32 +1544,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133828238</v>
+        <v>133828197</v>
       </c>
       <c r="B10" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1610,13 +1579,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519321</v>
+        <v>519032</v>
       </c>
       <c r="R10" t="n">
-        <v>6905895</v>
+        <v>6906144</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133828240</v>
+        <v>133828202</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,21 +1662,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519318</v>
+        <v>519066</v>
       </c>
       <c r="R11" t="n">
-        <v>6905855</v>
+        <v>6906112</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,7 +1721,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,12 +1731,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>35 ex</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133828230</v>
+        <v>133828208</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519227</v>
+        <v>519108</v>
       </c>
       <c r="R12" t="n">
-        <v>6905953</v>
+        <v>6906047</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1864,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,12 +1838,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133828203</v>
+        <v>133828235</v>
       </c>
       <c r="B13" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,13 +1900,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519084</v>
+        <v>519304</v>
       </c>
       <c r="R13" t="n">
-        <v>6906092</v>
+        <v>6905889</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,12 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133828209</v>
+        <v>133828239</v>
       </c>
       <c r="B14" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519108</v>
+        <v>519321</v>
       </c>
       <c r="R14" t="n">
-        <v>6906047</v>
+        <v>6905865</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,12 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 ex</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2079,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828196</v>
+        <v>133828213</v>
       </c>
       <c r="B15" t="n">
-        <v>83351</v>
+        <v>83341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2114,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519042</v>
+        <v>519134</v>
       </c>
       <c r="R15" t="n">
-        <v>6906192</v>
+        <v>6906052</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2149,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2159,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,32 +2186,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828214</v>
+        <v>133828189</v>
       </c>
       <c r="B16" t="n">
-        <v>80492</v>
+        <v>83358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2272,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519137</v>
+        <v>518990</v>
       </c>
       <c r="R16" t="n">
-        <v>6906050</v>
+        <v>6906250</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2307,7 +2256,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2266,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828199</v>
+        <v>133828196</v>
       </c>
       <c r="B17" t="n">
-        <v>89347</v>
+        <v>83358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2379,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519034</v>
+        <v>519042</v>
       </c>
       <c r="R17" t="n">
-        <v>6906130</v>
+        <v>6906192</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2414,7 +2363,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2373,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133828212</v>
+        <v>133828211</v>
       </c>
       <c r="B18" t="n">
-        <v>91967</v>
+        <v>83358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519127</v>
+        <v>519116</v>
       </c>
       <c r="R18" t="n">
-        <v>6906051</v>
+        <v>6906040</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2521,7 +2470,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2531,7 +2480,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,32 +2507,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133828236</v>
+        <v>133828220</v>
       </c>
       <c r="B19" t="n">
-        <v>98053</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519308</v>
+        <v>519131</v>
       </c>
       <c r="R19" t="n">
-        <v>6905887</v>
+        <v>6906030</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2628,7 +2577,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2587,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2614,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133828188</v>
+        <v>133828221</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>83358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,21 +2625,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2700,13 +2649,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518978</v>
+        <v>519140</v>
       </c>
       <c r="R20" t="n">
-        <v>6906255</v>
+        <v>6906024</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2735,7 +2684,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2745,7 +2694,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,32 +2721,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133828194</v>
+        <v>133828223</v>
       </c>
       <c r="B21" t="n">
-        <v>99188</v>
+        <v>83358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2807,13 +2756,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519039</v>
+        <v>519161</v>
       </c>
       <c r="R21" t="n">
-        <v>6906208</v>
+        <v>6906027</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2842,7 +2791,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2852,12 +2801,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>12 ex</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,32 +2828,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133828182</v>
+        <v>133828224</v>
       </c>
       <c r="B22" t="n">
-        <v>99188</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2919,13 +2863,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518967</v>
+        <v>519158</v>
       </c>
       <c r="R22" t="n">
-        <v>6906248</v>
+        <v>6906007</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2954,7 +2898,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2964,12 +2908,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>27 ex</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828356</v>
+        <v>133828233</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,42 +2946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518990</v>
+        <v>519272</v>
       </c>
       <c r="R23" t="n">
-        <v>6906191</v>
+        <v>6905906</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3074,7 +3005,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3084,12 +3015,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,7 +3045,7 @@
         <v>133828242</v>
       </c>
       <c r="B24" t="n">
-        <v>83351</v>
+        <v>83358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828216</v>
+        <v>133828198</v>
       </c>
       <c r="B25" t="n">
-        <v>80481</v>
+        <v>79130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,21 +3160,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3258,13 +3184,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519138</v>
+        <v>519034</v>
       </c>
       <c r="R25" t="n">
-        <v>6906045</v>
+        <v>6906126</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3293,7 +3219,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,7 +3229,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3330,10 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133828192</v>
+        <v>133828227</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3267,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519016</v>
+        <v>519206</v>
       </c>
       <c r="R26" t="n">
-        <v>6906224</v>
+        <v>6905965</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3400,7 +3326,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3410,7 +3336,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3437,32 +3363,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133828180</v>
+        <v>133828216</v>
       </c>
       <c r="B27" t="n">
-        <v>80486</v>
+        <v>80488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3472,13 +3398,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518951</v>
+        <v>519138</v>
       </c>
       <c r="R27" t="n">
-        <v>6906219</v>
+        <v>6906045</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3507,7 +3433,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3517,7 +3443,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133828227</v>
+        <v>133828237</v>
       </c>
       <c r="B28" t="n">
-        <v>79123</v>
+        <v>80488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,21 +3481,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3579,13 +3505,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519206</v>
+        <v>519323</v>
       </c>
       <c r="R28" t="n">
-        <v>6905965</v>
+        <v>6905894</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3614,7 +3540,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3550,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3651,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828193</v>
+        <v>133828238</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,45 +3588,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519027</v>
+        <v>519321</v>
       </c>
       <c r="R29" t="n">
-        <v>6906216</v>
+        <v>6905895</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3729,7 +3647,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3739,12 +3657,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3771,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828184</v>
+        <v>133828225</v>
       </c>
       <c r="B30" t="n">
-        <v>91930</v>
+        <v>80492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,21 +3695,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3806,13 +3719,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518977</v>
+        <v>519154</v>
       </c>
       <c r="R30" t="n">
-        <v>6906242</v>
+        <v>6905998</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3841,7 +3754,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3851,7 +3764,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,32 +3791,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828217</v>
+        <v>133828180</v>
       </c>
       <c r="B31" t="n">
-        <v>99188</v>
+        <v>80493</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3913,13 +3826,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519136</v>
+        <v>518951</v>
       </c>
       <c r="R31" t="n">
-        <v>6906039</v>
+        <v>6906219</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3948,7 +3861,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3958,12 +3871,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3990,32 +3898,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828198</v>
+        <v>133828195</v>
       </c>
       <c r="B32" t="n">
-        <v>79123</v>
+        <v>80493</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4025,13 +3933,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519034</v>
+        <v>519048</v>
       </c>
       <c r="R32" t="n">
-        <v>6906126</v>
+        <v>6906201</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4060,7 +3968,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4070,7 +3978,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,32 +4005,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133828235</v>
+        <v>133828204</v>
       </c>
       <c r="B33" t="n">
-        <v>79366</v>
+        <v>80493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4132,13 +4040,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519304</v>
+        <v>519091</v>
       </c>
       <c r="R33" t="n">
-        <v>6905889</v>
+        <v>6906091</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4167,7 +4075,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4177,7 +4085,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4204,53 +4112,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133828231</v>
+        <v>133828207</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519254</v>
+        <v>519112</v>
       </c>
       <c r="R34" t="n">
-        <v>6905931</v>
+        <v>6906067</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4282,7 +4182,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4292,12 +4192,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4324,32 +4219,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133828233</v>
+        <v>133828218</v>
       </c>
       <c r="B35" t="n">
-        <v>83351</v>
+        <v>80493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4359,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519272</v>
+        <v>519135</v>
       </c>
       <c r="R35" t="n">
-        <v>6905906</v>
+        <v>6906035</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4394,7 +4289,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4404,7 +4299,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4431,27 +4326,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133828197</v>
+        <v>133828214</v>
       </c>
       <c r="B36" t="n">
-        <v>79366</v>
+        <v>80499</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4466,10 +4361,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519032</v>
+        <v>519137</v>
       </c>
       <c r="R36" t="n">
-        <v>6906144</v>
+        <v>6906050</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4501,7 +4396,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4511,7 +4406,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4538,45 +4433,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133828218</v>
+        <v>133828187</v>
       </c>
       <c r="B37" t="n">
-        <v>80486</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519135</v>
+        <v>518978</v>
       </c>
       <c r="R37" t="n">
-        <v>6906035</v>
+        <v>6906255</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4608,7 +4511,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4618,7 +4521,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4645,48 +4553,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133828207</v>
+        <v>133828190</v>
       </c>
       <c r="B38" t="n">
-        <v>80486</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519112</v>
+        <v>519017</v>
       </c>
       <c r="R38" t="n">
-        <v>6906067</v>
+        <v>6906239</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4715,7 +4631,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4725,7 +4641,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,45 +4673,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133828241</v>
+        <v>133828193</v>
       </c>
       <c r="B39" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519330</v>
+        <v>519027</v>
       </c>
       <c r="R39" t="n">
-        <v>6905844</v>
+        <v>6906216</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4822,7 +4751,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4832,12 +4761,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4864,45 +4793,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133828226</v>
+        <v>133828201</v>
       </c>
       <c r="B40" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519204</v>
+        <v>519061</v>
       </c>
       <c r="R40" t="n">
-        <v>6905970</v>
+        <v>6906118</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4934,7 +4871,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4944,12 +4881,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4976,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133828222</v>
+        <v>133828205</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4987,34 +4924,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519147</v>
+        <v>519093</v>
       </c>
       <c r="R41" t="n">
-        <v>6906035</v>
+        <v>6906086</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5046,7 +4991,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5056,7 +5001,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5083,48 +5033,56 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133828191</v>
+        <v>133828210</v>
       </c>
       <c r="B42" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519018</v>
+        <v>519112</v>
       </c>
       <c r="R42" t="n">
-        <v>6906233</v>
+        <v>6906042</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,7 +5111,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5163,12 +5121,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5195,45 +5153,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133828232</v>
+        <v>133828231</v>
       </c>
       <c r="B43" t="n">
-        <v>80431</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519261</v>
+        <v>519254</v>
       </c>
       <c r="R43" t="n">
-        <v>6905908</v>
+        <v>6905931</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5265,7 +5231,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5275,7 +5241,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5302,10 +5273,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133828239</v>
+        <v>133828355</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,34 +5284,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519321</v>
+        <v>518990</v>
       </c>
       <c r="R44" t="n">
-        <v>6905865</v>
+        <v>6906188</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5372,7 +5351,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5382,7 +5361,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5409,48 +5393,56 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133828186</v>
+        <v>133828356</v>
       </c>
       <c r="B45" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518978</v>
+        <v>518990</v>
       </c>
       <c r="R45" t="n">
-        <v>6906247</v>
+        <v>6906191</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5479,7 +5471,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5489,12 +5481,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5521,56 +5513,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133828205</v>
+        <v>133828181</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519093</v>
+        <v>518950</v>
       </c>
       <c r="R46" t="n">
-        <v>6906086</v>
+        <v>6906228</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5599,7 +5583,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5609,12 +5593,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5641,56 +5625,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133828187</v>
+        <v>133828182</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518978</v>
+        <v>518967</v>
       </c>
       <c r="R47" t="n">
-        <v>6906255</v>
+        <v>6906248</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5719,7 +5695,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5729,12 +5705,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5761,32 +5737,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133828234</v>
+        <v>133828186</v>
       </c>
       <c r="B48" t="n">
-        <v>80431</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5796,10 +5772,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519302</v>
+        <v>518978</v>
       </c>
       <c r="R48" t="n">
-        <v>6905898</v>
+        <v>6906247</v>
       </c>
       <c r="S48" t="n">
         <v>6</v>
@@ -5831,7 +5807,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5841,7 +5817,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5868,32 +5849,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133828183</v>
+        <v>133828191</v>
       </c>
       <c r="B49" t="n">
-        <v>91967</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5903,10 +5884,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518971</v>
+        <v>519018</v>
       </c>
       <c r="R49" t="n">
-        <v>6906249</v>
+        <v>6906233</v>
       </c>
       <c r="S49" t="n">
         <v>6</v>
@@ -5938,7 +5919,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5948,7 +5929,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5975,32 +5961,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133828211</v>
+        <v>133828194</v>
       </c>
       <c r="B50" t="n">
-        <v>83351</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6010,13 +5996,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519116</v>
+        <v>519039</v>
       </c>
       <c r="R50" t="n">
-        <v>6906040</v>
+        <v>6906208</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6045,7 +6031,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6055,7 +6041,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>12 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6082,32 +6073,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133828223</v>
+        <v>133828200</v>
       </c>
       <c r="B51" t="n">
-        <v>83351</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6117,13 +6108,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519161</v>
+        <v>519034</v>
       </c>
       <c r="R51" t="n">
-        <v>6906027</v>
+        <v>6906128</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6152,7 +6143,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6162,7 +6153,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,53 +6185,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133828210</v>
+        <v>133828203</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519112</v>
+        <v>519084</v>
       </c>
       <c r="R52" t="n">
-        <v>6906042</v>
+        <v>6906092</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6267,7 +6255,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6277,12 +6265,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6309,53 +6297,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133828355</v>
+        <v>133828206</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518990</v>
+        <v>519089</v>
       </c>
       <c r="R53" t="n">
-        <v>6906188</v>
+        <v>6906079</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6387,7 +6367,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6397,12 +6377,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,32 +6409,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133828189</v>
+        <v>133828209</v>
       </c>
       <c r="B54" t="n">
-        <v>83351</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6464,10 +6444,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518990</v>
+        <v>519108</v>
       </c>
       <c r="R54" t="n">
-        <v>6906250</v>
+        <v>6906047</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6499,7 +6479,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6509,7 +6489,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6536,32 +6521,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133828204</v>
+        <v>133828217</v>
       </c>
       <c r="B55" t="n">
-        <v>80486</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6571,10 +6556,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519091</v>
+        <v>519136</v>
       </c>
       <c r="R55" t="n">
-        <v>6906091</v>
+        <v>6906039</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6606,7 +6591,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6616,7 +6601,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6643,32 +6633,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133828237</v>
+        <v>133828226</v>
       </c>
       <c r="B56" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6678,13 +6668,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519323</v>
+        <v>519204</v>
       </c>
       <c r="R56" t="n">
-        <v>6905894</v>
+        <v>6905970</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6713,7 +6703,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6723,7 +6713,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6750,10 +6745,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133828181</v>
+        <v>133828230</v>
       </c>
       <c r="B57" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6785,13 +6780,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518950</v>
+        <v>519227</v>
       </c>
       <c r="R57" t="n">
-        <v>6906228</v>
+        <v>6905953</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6820,7 +6815,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6830,7 +6825,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6862,32 +6857,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133828202</v>
+        <v>133828240</v>
       </c>
       <c r="B58" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6897,10 +6892,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519066</v>
+        <v>519318</v>
       </c>
       <c r="R58" t="n">
-        <v>6906112</v>
+        <v>6905855</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6932,7 +6927,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6942,7 +6937,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6969,32 +6969,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133828221</v>
+        <v>133828241</v>
       </c>
       <c r="B59" t="n">
-        <v>83351</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519140</v>
+        <v>519330</v>
       </c>
       <c r="R59" t="n">
-        <v>6906024</v>
+        <v>6905844</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7049,7 +7049,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7076,32 +7081,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133828200</v>
+        <v>133828236</v>
       </c>
       <c r="B60" t="n">
-        <v>99188</v>
+        <v>98060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7111,13 +7116,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519034</v>
+        <v>519308</v>
       </c>
       <c r="R60" t="n">
-        <v>6906128</v>
+        <v>6905887</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7146,7 +7151,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7156,12 +7161,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7188,10 +7188,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133828220</v>
+        <v>133828222</v>
       </c>
       <c r="B61" t="n">
-        <v>83351</v>
+        <v>79131</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7199,21 +7199,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7223,10 +7223,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519131</v>
+        <v>519147</v>
       </c>
       <c r="R61" t="n">
-        <v>6906030</v>
+        <v>6906035</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7292,6 +7292,220 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133828232</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Grundvattsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>519261</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6905908</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133828234</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grundvattsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>519302</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6905898</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24423-2026 artfynd.xlsx
+++ b/artfynd/A 24423-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828244</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828199</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828183</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828212</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828188</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828192</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828197</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828202</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828235</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2076,6 +2141,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828239</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828213</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828189</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2397,6 +2477,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828196</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2611,6 +2701,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828220</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2718,6 +2813,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828221</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2825,6 +2925,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828223</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2932,6 +3037,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828224</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3039,6 +3149,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828233</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3146,6 +3261,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828242</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3253,6 +3373,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828198</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3360,6 +3485,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828227</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3467,6 +3597,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828216</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3574,6 +3709,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828237</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3681,6 +3821,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828238</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3788,6 +3933,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828225</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3895,6 +4045,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828180</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4002,6 +4157,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828195</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4109,6 +4269,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828204</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4216,6 +4381,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828207</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4323,6 +4493,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828218</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4430,6 +4605,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828214</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4550,6 +4730,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828187</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4670,6 +4855,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828190</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4790,6 +4980,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828193</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4910,6 +5105,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828201</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5030,6 +5230,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828205</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5150,6 +5355,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828210</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5270,6 +5480,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828231</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5390,6 +5605,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828355</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5510,6 +5730,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828356</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5622,6 +5847,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828181</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5734,6 +5964,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828182</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5846,6 +6081,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828186</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5958,6 +6198,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828191</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6070,6 +6315,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828194</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6182,6 +6432,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828200</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6294,6 +6549,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828203</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6406,6 +6666,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828206</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6518,6 +6783,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828209</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6630,6 +6900,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828217</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6742,6 +7017,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828226</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6854,6 +7134,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828230</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6966,6 +7251,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828240</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7078,6 +7368,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828241</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7185,6 +7480,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828236</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7292,6 +7592,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828222</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7399,6 +7704,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828232</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7506,8 +7816,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133828234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>